--- a/agent-workbench/TRACKER.xlsx
+++ b/agent-workbench/TRACKER.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -581,24 +581,24 @@
           <t>Stage 0 - Owner decision: Windows guest licence (90-day Enterprise evaluation ISO vs bought licence)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Decided 10-10-2026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Zero-cost pilot path is the evaluation ISO; it expires. See README section 'Risks the Boss may not be seeing'.</t>
+          <t>DECIDED by the Architect, confirmed in Ravi's handover: 90-day Windows 11 Enterprise evaluation ISO for the pilot. Expires after 90 days; rebuild or license then.</t>
         </is>
       </c>
     </row>
@@ -611,24 +611,24 @@
           <t>Stage 0 - Owner decision: which drive holds the VHDX (not C:)</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Decided 10-10-2026</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Owner, after preflight prints the drives</t>
+          <t>Confirm with preflight numbers</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Preflight recommends the fixed drive with most free space, needs &gt;= 100 GB free.</t>
+          <t>DECIDED: E: if it is a healthy fixed drive with enough free space, otherwise D:. Never C:. Preflight must print the numbers before New-Workbench runs.</t>
         </is>
       </c>
     </row>
@@ -911,14 +911,14 @@
           <t>Stage 4 - Production protection: guest-only credentials, no host drive shares, no production DB from guest</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 session</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Default Switch gives guest internet via NAT; it does NOT expose host drives. Rules in README.</t>
+          <t>Done in code: /shell is OFF unless the guest service is started with --enable-shell; service accepts only localhost + the host (default gateway), 403 to others; firewall rule limited to the host address. Still owed: block guest -&gt; LAN (RFC1918) at the host firewall, guest-only Git identity.</t>
         </is>
       </c>
     </row>
@@ -1109,6 +1109,216 @@
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Placement law. This cloud session only reaches the public sehgalautoriders/avni repo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Review round 1 - F1 Critical: hands service reachable by any client on the virtual network</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1 session (10-10-2026)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Verify in guest</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Service now refuses every client except localhost and the default gateway (= the host on Default Switch) with 403 BEFORE the token check; --allow-client / --allow-any-client to widen on purpose. Installer firewall rule limited to -RemoteAddress &lt;gateway&gt;. 13 new unit tests pass on Linux. Token still travels over plain HTTP on the host-guest link: accepted for the pilot, noted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Review round 1 - F2 High: screenshots and run records land on C:</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1 session</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Set AVNI_WORKBENCH_DATA on the host in Stage 1</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Driver: run folders go to %AVNI_WORKBENCH_DATA%\runs when that variable is set (point it at the approved drive), else %LOCALAPPDATA%. Guest: archive capped by --archive-max-mb (default 2048), oldest frames removed, only files the service itself named. Guest archive lives inside the VHDX, which is already on the approved drive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Review round 1 - F3 High: /shell arbitrary commands, Default Switch is not production isolation</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1 session</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Stage 4 before real project work</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Done: /shell off by default (--enable-shell), PAUSE file now kills a running shell command (tested: aborted in &lt;1 s). Owed: host firewall rule blocking the Default Switch subnet from reaching the LAN (RFC1918) while allowing internet; guest-only Git deploy key.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Review round 1 - F4 Medium: VM creation changed host-wide Enhanced Session Mode</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1 session</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Parse-checked only</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>New-Workbench.ps1 now measures the setting and reports it; changes it only with -EnableEnhancedSession.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Review round 1 - F5 Medium: driver TypeError on API errors (kind passed twice)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1 session</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Real bug, confirmed in code. Renamed to error_kind. pyflakes clean; the dry-run path re-ran green. The live-API error path is still UNVERIFIED (needs a real API call).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Register the Workbench in AVNI Sentinel as 'installed but OFF' (never a permanently running process)</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Next local session</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Architect rule 10-10-2026. Needs the AEBrain tree; not reachable from the cloud session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Read-only viewer so clicking in the window never steals Ravi's keyboard</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Worker card WC-03</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Architect flagged again. Until built: watch in vmconnect, do not click inside.</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1238,6 +1448,18 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10-10-2026 review round 1 (Architect findings F1-F5), items 21-27 added, 3 and 4 decided</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/agent-workbench/TRACKER.xlsx
+++ b/agent-workbench/TRACKER.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -618,17 +618,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Decided 10-10-2026</t>
+          <t>Decided 18-10-2026</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Confirm with preflight numbers</t>
+          <t>Select after preflight</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>DECIDED: E: if it is a healthy fixed drive with enough free space, otherwise D:. Never C:. Preflight must print the numbers before New-Workbench runs.</t>
+          <t>DECIDED (Architect 18-10-2026): choose only after preflight from measured, suitable fixed drives. C: untouched. The SSD reserved for AVNI OS is EXCLUDED. The 2 TB HDD is the candidate if preflight shows it healthy, with free space and acceptable performance. Never guess the letter.</t>
         </is>
       </c>
     </row>
@@ -918,17 +918,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1 session</t>
+          <t>2 sessions</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Before first real project work</t>
+          <t>Apply before first connected boot</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Done in code: /shell is OFF unless the guest service is started with --enable-shell; service accepts only localhost + the host (default gateway), 403 to others; firewall rule limited to the host address. Still owed: block guest -&gt; LAN (RFC1918) at the host firewall, guest-only Git identity.</t>
+          <t>DECIDED (Architect 18-10-2026): guest-to-LAN block comes BEFORE the first network-connected guest boot. Mechanism: Hyper-V Extended Port ACLs on the VM adapter (host-enforced, the guest cannot lift them). Scripts: host/Set-WorkbenchNetworkIsolation.ps1 (Apply/Show/Remove/Connect/Disconnect) and host/Test-WorkbenchIsolation.ps1 (PowerShell Direct proof from inside the guest). New-Workbench now creates the adapter DISCONNECTED. Guest-only Git identity still owed.</t>
         </is>
       </c>
     </row>
@@ -1188,17 +1188,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1 session</t>
+          <t>2 sessions</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Stage 4 before real project work</t>
+          <t>Verify on PC</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Done: /shell off by default (--enable-shell), PAUSE file now kills a running shell command (tested: aborted in &lt;1 s). Owed: host firewall rule blocking the Default Switch subnet from reaching the LAN (RFC1918) while allowing internet; guest-only Git deploy key.</t>
+          <t>Code done 18-10-2026: Extended Port ACLs deny RFC1918 + link-local in and out, allow the Default Switch gateway (host) only, public internet stays open; Connect refuses unless deny rules are present. UNVERIFIED on Hyper-V until the local session runs Apply then Test.</t>
         </is>
       </c>
     </row>
@@ -1319,6 +1319,126 @@
       <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Architect flagged again. Until built: watch in vmconnect, do not click inside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Resume prompt for the LOCAL session (exact order: preflight -&gt; drive -&gt; create offline -&gt; isolate -&gt; connect -&gt; Windows setup -&gt; hands -&gt; dry run -&gt; demos)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>18-10-2026</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>agent-workbench/RESUME-LOCAL-SESSION.md. Paste into Claude Code on the PC. Carries all decisions so nothing is asked again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Milestone ledger: DESIGNED / CODED / TESTED / INSTALLED / VERIFIED per component</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>18-10-2026</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Local session fills INSTALLED/VERIFIED</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Table in RESUME-LOCAL-SESSION.md section 2. Nothing is INSTALLED or VERIFIED yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Evaluate the 2 TB HDD: health (SMART / Get-PhysicalDisk HealthStatus), free space, sequential and random performance (winsat disk or a 1 GB write/read timing) before it hosts the VHDX</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Local session, 10 min</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Architect 18-10-2026: evaluate performance, not only capacity. A VHDX on a slow HDD makes the guest desktop sluggish; preflight numbers decide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Release / version ledger entry with exact evidence, commit, install status, remaining failures</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Local session after first VERIFIED milestone</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Architect 18-10-2026. Ledger lives in the AEBrain tree; not reachable from the cloud session.</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1460,6 +1580,18 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>18-10-2026 Architect decisions: drive after preflight (exclude C: and AVNI OS SSD, 2 TB HDD candidate), LAN block before first connected boot; items 28-31 added</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/agent-workbench/TRACKER.xlsx
+++ b/agent-workbench/TRACKER.xlsx
@@ -1198,7 +1198,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Code done 18-10-2026: Extended Port ACLs deny RFC1918 + link-local in and out, allow the Default Switch gateway (host) only, public internet stays open; Connect refuses unless deny rules are present. UNVERIFIED on Hyper-V until the local session runs Apply then Test.</t>
+          <t>Code done 18-10-2026: Extended Port ACLs deny RFC1918 + link-local + IPv6 ULA/link-local in and out; guest may reach the host (Default Switch gateway) ONLY for DNS (53) and hands-service replies, so host SMB/RDP/dev servers stay unreachable from the guest; public internet stays open; Connect refuses unless the deny rules are present and the gateway is unchanged. Test-WorkbenchIsolation.ps1 proves it over PowerShell Direct. UNVERIFIED on Hyper-V until the local session runs Apply then Test. Known: Default Switch subnet can change after a host reboot; re-Apply then.</t>
         </is>
       </c>
     </row>

--- a/agent-workbench/TRACKER.xlsx
+++ b/agent-workbench/TRACKER.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>host/Preflight-Workbench.ps1. Parse-checked with PowerShell 7 on Linux only. CONFIGURED - UNVERIFIED until it runs on the real PC.</t>
+          <t>Plain run on the PC 19-10-2026 09:06: READY WITH CONDITIONS. Hyper-V not installed (no vmms, no module), hypervisor on (VBS). RAM 31.3/10.2 GB free -&gt; 6 GB VM. Elevated re-run waits for the Hyper-V permission. See PREFLIGHT-19-10-2026.md</t>
         </is>
       </c>
     </row>
@@ -611,9 +611,9 @@
           <t>Stage 0 - Owner decision: which drive holds the VHDX (not C:)</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>DECIDED (Architect 18-10-2026): choose only after preflight from measured, suitable fixed drives. C: untouched. The SSD reserved for AVNI OS is EXCLUDED. The 2 TB HDD is the candidate if preflight shows it healthy, with free space and acceptable performance. Never guess the letter.</t>
+          <t>Rule decided 18-10; measured 19-10: only C: (system) and E: (USB SanDisk SSD, kept for AVNI OS) are connected. 2 TB HDD absent -&gt; no drive chosen, nothing allocated</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Architect 18-10-2026: evaluate performance, not only capacity. A VHDX on a slow HDD makes the guest desktop sluggish; preflight numbers decide.</t>
+          <t>19-10-2026: 2 TB HDD not connected to the PC (Get-PhysicalDisk shows only disk 0 NVMe + disk 1 SanDisk USB). Owner to plug it in</t>
         </is>
       </c>
     </row>

--- a/agent-workbench/TRACKER.xlsx
+++ b/agent-workbench/TRACKER.xlsx
@@ -553,22 +553,23 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>1 session</t>
+          <t>17 s plain + 41 s elevated</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Run on PC: next local session, 5 min</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Plain run on the PC 19-10-2026 09:06: READY WITH CONDITIONS. Hyper-V not installed (no vmms, no module), hypervisor on (VBS). RAM 31.3/10.2 GB free -&gt; 6 GB VM. Elevated re-run waits for the Hyper-V permission. See PREFLIGHT-19-10-2026.md</t>
+          <t>21-10-2026: plain run 17:49 and ELEVATED run 17:50 (UAC pressed by Ravi at the PC) - both READY WITH CONDITIONS. Measured: Microsoft-Hyper-V-All = Disabled; no Hyper-V module, no vmms; hypervisor present (VBS). RAM 63.3 GB total / 29.8 GB free -&gt; 8 GB VM. Fixed drives: C: 57.7 GB free (system, excluded), E: 845.9 GB free. Then 17:52 elevated: Enable-WindowsOptionalFeature Microsoft-Hyper-V-All -NoRestart -&gt; all 7 Hyper-V features Enabled, RestartNeeded = True (completes at the next power-off). Raw reports on the PC only: %LOCALAPPDATA%\Avni+eports\workbench-preflight-21-10-2026_1749 / _1750 and workbench-hyperv-enable-21-10-2026.log. See PREFLIGHT-21-10-2026.md</t>
         </is>
       </c>
     </row>
@@ -613,7 +614,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -628,7 +629,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Rule decided 18-10; measured 19-10: only C: (system) and E: (USB SanDisk SSD, kept for AVNI OS) are connected. 2 TB HDD absent -&gt; no drive chosen, nothing allocated</t>
+          <t>Rule decided 18-10; measured 19-10: only C: (system) and E: (USB SanDisk SSD, kept for AVNI OS) are connected. 2 TB HDD absent -&gt; no drive chosen, nothing allocated | 20-10-2026 14:38 Ravi (phone ask-33c40ae475724999): 'I will plug in the 2 TB disk and allow Hyper-V'. 21-10-2026 17:4x: Hyper-V allowed and switched on; the 2 TB disk is still not connected (only C: and E:). No drive chosen, nothing allocated.</t>
         </is>
       </c>
     </row>
@@ -643,7 +644,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -733,7 +734,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -763,7 +764,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -793,7 +794,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -853,7 +854,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -883,7 +884,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -913,7 +914,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1153,7 +1154,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1183,7 +1184,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1393,7 +1394,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1408,7 +1409,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19-10-2026: 2 TB HDD not connected to the PC (Get-PhysicalDisk shows only disk 0 NVMe + disk 1 SanDisk USB). Owner to plug it in</t>
+          <t>19-10-2026: 2 TB HDD not connected to the PC (Get-PhysicalDisk shows only disk 0 NVMe + disk 1 SanDisk USB). Owner to plug it in | 21-10-2026 17:4x: still not connected (Get-Disk: 0 Samsung NVMe, 1 SanDisk USB).</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1488,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Built, not yet verified where it must run. CONFIGURED - UNVERIFIED.</t>
+          <t>Started, not finished (Ravi 20-10-2026: the word 'partial' is not used anywhere in AVNI)</t>
         </is>
       </c>
     </row>
@@ -1544,6 +1545,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>

--- a/agent-workbench/TRACKER.xlsx
+++ b/agent-workbench/TRACKER.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>guest/avni_hands.py. Pure-logic parts unit-tested on Linux; user32/SendInput path UNVERIFIED until run in the guest.</t>
+          <t>guest/avni_hands.py. Pure-logic parts unit-tested on Linux; user32/SendInput path UNVERIFIED until run in the guest. | 21-10-2026 18:09 TESTED on the PC (Windows, Python 3.14, Pillow + pywin32 installed): unittest discover guest/ -&gt; 54 ran, 0 failures, 4 skipped. Not yet installed in a guest (no VM yet).</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>host/workbench_driver.py. Tested on Linux only against the hands service in --dry-run mode.</t>
+          <t>host/workbench_driver.py. Tested on Linux only against the hands service in --dry-run mode. | 21-10-2026 18:09 TESTED on the PC (Windows, Python 3.14, Pillow + pywin32 installed): unittest discover guest/ -&gt; 54 ran, 0 failures, 4 skipped. Not yet installed in a guest (no VM yet).</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Service now refuses every client except localhost and the default gateway (= the host on Default Switch) with 403 BEFORE the token check; --allow-client / --allow-any-client to widen on purpose. Installer firewall rule limited to -RemoteAddress &lt;gateway&gt;. 13 new unit tests pass on Linux. Token still travels over plain HTTP on the host-guest link: accepted for the pilot, noted.</t>
+          <t>Service now refuses every client except localhost and the default gateway (= the host on Default Switch) with 403 BEFORE the token check; --allow-client / --allow-any-client to widen on purpose. Installer firewall rule limited to -RemoteAddress &lt;gateway&gt;. 13 new unit tests pass on Linux. Token still travels over plain HTTP on the host-guest link: accepted for the pilot, noted. | 21-10-2026 18:09 TESTED on the PC (Windows, Python 3.14, Pillow + pywin32 installed): unittest discover guest/ -&gt; 54 ran, 0 failures, 4 skipped. Not yet installed in a guest (no VM yet).</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>

--- a/agent-workbench/TRACKER.xlsx
+++ b/agent-workbench/TRACKER.xlsx
@@ -809,7 +809,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>host/workbench_driver.py. Tested on Linux only against the hands service in --dry-run mode. | 21-10-2026 18:09 TESTED on the PC (Windows, Python 3.14, Pillow + pywin32 installed): unittest discover guest/ -&gt; 54 ran, 0 failures, 4 skipped. Not yet installed in a guest (no VM yet).</t>
+          <t>host/workbench_driver.py. Tested on Linux only against the hands service in --dry-run mode.</t>
         </is>
       </c>
     </row>

--- a/agent-workbench/TRACKER.xlsx
+++ b/agent-workbench/TRACKER.xlsx
@@ -614,22 +614,23 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Decided 18-10-2026</t>
+          <t>Decided 21-10-2026</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Select after preflight</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Rule decided 18-10; measured 19-10: only C: (system) and E: (USB SanDisk SSD, kept for AVNI OS) are connected. 2 TB HDD absent -&gt; no drive chosen, nothing allocated | 20-10-2026 14:38 Ravi (phone ask-33c40ae475724999): 'I will plug in the 2 TB disk and allow Hyper-V'. 21-10-2026 17:4x: Hyper-V allowed and switched on; the 2 TB disk is still not connected (only C: and E:). No drive chosen, nothing allocated.</t>
+          <t>Rule decided 18-10; measured 19-10: only C: (system) and E: (USB SanDisk SSD, kept for AVNI OS) are connected. 2 TB HDD absent -&gt; no drive chosen, nothing allocated | 20-10-2026 14:38 Ravi (phone ask-33c40ae475724999): 'I will plug in the 2 TB disk and allow Hyper-V'. 21-10-2026 17:4x: Hyper-V allowed and switched on; the 2 TB disk is still not connected (only C: and E:). No drive chosen, nothing allocated. | 21-10-2026 18:2x RAVI: 'There will be no HDD 2 TB, 1 TB SSD is attached' + 'All programs stay on C only. Files from top priority to 1 which the program needs immediately stay on C. Others move to E.' DECISION: VM data (VHDX, checkpoints, ISO) on E:\AVNI-Workbench\ (E: = the detachable overflow drive by the C-to-E law; the Workbench is OFF by default and rebuildable from the ISO; C: has 58 GB free, below the 100 GB floor, so it cannot hold a VHDX). Programs (scripts, hands service, driver, run folders) stay on C:. AVNI_WORKBENCH_DATA (User) = %LOCALAPPDATA%\Avni\workbench+uns.</t>
         </is>
       </c>
     </row>
@@ -1389,27 +1390,27 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Evaluate the 2 TB HDD: health (SMART / Get-PhysicalDisk HealthStatus), free space, sequential and random performance (winsat disk or a 1 GB write/read timing) before it hosts the VHDX</t>
+          <t>Evaluate the Workbench drive (was: the 2 TB HDD; since 21-10-2026 the 1 TB SanDisk SSD E:): health, free space, timed 1 GB write/read before it hosts the VHDX</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4 min</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Local session, 10 min</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19-10-2026: 2 TB HDD not connected to the PC (Get-PhysicalDisk shows only disk 0 NVMe + disk 1 SanDisk USB). Owner to plug it in | 21-10-2026 17:4x: still not connected (Get-Disk: 0 Samsung NVMe, 1 SanDisk USB).</t>
+          <t>19-10-2026: 2 TB HDD not connected to the PC (Get-PhysicalDisk shows only disk 0 NVMe + disk 1 SanDisk USB). Owner to plug it in | 21-10-2026 17:4x: still not connected (Get-Disk: 0 Samsung NVMe, 1 SanDisk USB). | 21-10-2026 18:29 MEASURED on E: (SanDisk Extreme 55DD, USB, SSD): HealthStatus Healthy, OperationalStatus OK, 931.5 GB / 839 GB free; 1 GB write with WriteThrough 68.5 s = 15 MB/s; 1 GB buffered write + Flush(true) 34.3 s = 30 MB/s; read of the same file 0.6 s = cache, not the disk. Reliability counters not exposed over USB. 30 MB/s is USB-2 class - the port/cable is being checked; the VM will work but Windows setup will be slow.</t>
         </is>
       </c>
     </row>

--- a/agent-workbench/TRACKER.xlsx
+++ b/agent-workbench/TRACKER.xlsx
@@ -645,22 +645,22 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1 session</t>
+          <t>35 s</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Local session, 10 min after decisions 3 and 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>host/New-Workbench.ps1 written, parse-checked only. Needs admin PowerShell on the PC.</t>
+          <t>host/New-Workbench.ps1 written, parse-checked only. Needs admin PowerShell on the PC. | 21-10-2026 18:46 INSTALLED on the PC (elevated New-Workbench.ps1 -VhdRoot E:\AVNI-Workbench\AVNI-VMs): Gen 2, dynamic VHDX 200 GB (0 GB on disk), memory 6 start / 2 min / 8 max GB dynamic, 4 vCPU, Secure Boot MicrosoftWindows, vTPM, Guest Service Interface on, adapter disconnected, AutomaticStartAction Nothing, State Off. Record %LOCALAPPDATA%\Avni\reports\workbench-create-21-10-2026_1845.json. No ISO attached yet (download in progress).</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Windows setup needs a human at the console for the pilot. Steps printed by New-Workbench.ps1.</t>
+          <t>Windows setup needs a human at the console for the pilot. Steps printed by New-Workbench.ps1. | 21-10-2026: planned UNATTENDED, not by hand - autounattend.xml (local account, OOBE hidden, India time zone, UEFI partitions, image index 1) built into E:\AVNI-Workbench\iso\autounattend.iso (IMAPI2, no ADK); the guest account record stays on the PC only (%LOCALAPPDATA%\Avni\workbench\guest-account.json, never committed). Waits for the Windows ISO (8.2 GB) to finish.</t>
         </is>
       </c>
     </row>
@@ -1185,22 +1185,22 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2 sessions</t>
+          <t>2 runs</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify on PC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Code done 18-10-2026: Extended Port ACLs deny RFC1918 + link-local + IPv6 ULA/link-local in and out; guest may reach the host (Default Switch gateway) ONLY for DNS (53) and hands-service replies, so host SMB/RDP/dev servers stay unreachable from the guest; public internet stays open; Connect refuses unless the deny rules are present and the gateway is unchanged. Test-WorkbenchIsolation.ps1 proves it over PowerShell Direct. UNVERIFIED on Hyper-V until the local session runs Apply then Test. Known: Default Switch subnet can change after a host reboot; re-Apply then.</t>
+          <t>Code done 18-10-2026: Extended Port ACLs deny RFC1918 + link-local + IPv6 ULA/link-local in and out; guest may reach the host (Default Switch gateway) ONLY for DNS (53) and hands-service replies, so host SMB/RDP/dev servers stay unreachable from the guest; public internet stays open; Connect refuses unless the deny rules are present and the gateway is unchanged. Test-WorkbenchIsolation.ps1 proves it over PowerShell Direct. UNVERIFIED on Hyper-V until the local session runs Apply then Test. Known: Default Switch subnet can change after a host reboot; re-Apply then. | 21-10-2026 18:49 first Connect FAILED: Hyper-V 0x800700B7 'Cannot create a file when that file already exists' - proven by an elevated test (18:5x) to be two Extended ACL rules with the same Direction+Weight on a live switch port; unique weights and IPv6 rules are accepted. Fix: Set-WorkbenchNetworkIsolation.ps1 1.1.0 gives every rule its own weight (Outbound deny 50-56, Inbound deny 40-46, host 60+, ExtraAllow 80+, Inbound hands 101) and refuses a plan with a duplicate before touching the switch. 18:58 run 2: Apply 21 rules read back, Show inventory MATCHES, Connect -&gt; SwitchName Default Switch, Connected True, VM Off. Behaviour proof (Test-WorkbenchIsolation.ps1) still pending until the guest runs.</t>
         </is>
       </c>
     </row>

--- a/agent-workbench/TRACKER.xlsx
+++ b/agent-workbench/TRACKER.xlsx
@@ -810,7 +810,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>host/workbench_driver.py. Tested on Linux only against the hands service in --dry-run mode.</t>
+          <t>host/workbench_driver.py. Tested on Linux only against the hands service in --dry-run mode. | 21-10-2026 19:12 TESTED on the PC (Windows): hands service 0.2.0 started on the host loopback in --dry-run (logs input, injects nothing), workbench_driver.py --dry-run-model against it -&gt; 14 actions, 0 unexpected failures, exit 0 in 3 s, run record in the scratch run folder. Not yet against the real guest (step H).</t>
         </is>
       </c>
     </row>

--- a/agent-workbench/TRACKER.xlsx
+++ b/agent-workbench/TRACKER.xlsx
@@ -675,22 +675,22 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>boot 20:16, answered 23:42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Human clicks, ~40 min</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Windows setup needs a human at the console for the pilot. Steps printed by New-Workbench.ps1. | 21-10-2026: planned UNATTENDED, not by hand - autounattend.xml (local account, OOBE hidden, India time zone, UEFI partitions, image index 1) built into E:\AVNI-Workbench\iso\autounattend.iso (IMAPI2, no ADK); the guest account record stays on the PC only (%LOCALAPPDATA%\Avni\workbench\guest-account.json, never committed). Waits for the Windows ISO (8.2 GB) to finish.</t>
+          <t>Windows setup needs a human at the console for the pilot. Steps printed by New-Workbench.ps1. | 21-10-2026: planned UNATTENDED, not by hand - autounattend.xml (local account, OOBE hidden, India time zone, UEFI partitions, image index 1) built into E:\AVNI-Workbench\iso\autounattend.iso (IMAPI2, no ADK); the guest account record stays on the PC only (%LOCALAPPDATA%\Avni\workbench\guest-account.json, never committed). Waits for the Windows ISO (8.2 GB) to finish. | 21-10-2026 INSTALLED UNATTENDED: ISO (8,225,329,152 bytes, mounted + sources\install.wim checked) + autounattend.iso attached as DVDs, DVD first in the boot order, Start-VM 20:16, Enter sent through WMI Msvm_Keyboard.TypeKey for the 'Press any key' prompt (33 accepted), nobody clicked in vmconnect. Host power-off/boot at 22:36 switched the VM Off mid-way; minder restarted it 23:32; first-run 'Just a moment' until 23:42, then the guest answered PowerShell Direct as AVNI-WB01\agent, OOBEInProgress=0, explorer running. VHDX 16.6 GB. Checkpoint '21-10-2026 2342 clean install' created 23:43:56 (Workbench.ps1 -Action Checkpoint). Guest thumbnails via WMI GetVirtualSystemThumbnailImage in %LOCALAPPDATA%\Avni\workbench\runs\.</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>host/Workbench.ps1 parse-checked only.</t>
+          <t>host/Workbench.ps1 parse-checked only. | 21-10-2026 23:43 Checkpoint action USED on the PC: created and read back (Get-VMSnapshot). Status/Start/Ip/Connect still to be exercised.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Code done 18-10-2026: Extended Port ACLs deny RFC1918 + link-local + IPv6 ULA/link-local in and out; guest may reach the host (Default Switch gateway) ONLY for DNS (53) and hands-service replies, so host SMB/RDP/dev servers stay unreachable from the guest; public internet stays open; Connect refuses unless the deny rules are present and the gateway is unchanged. Test-WorkbenchIsolation.ps1 proves it over PowerShell Direct. UNVERIFIED on Hyper-V until the local session runs Apply then Test. Known: Default Switch subnet can change after a host reboot; re-Apply then. | 21-10-2026 18:49 first Connect FAILED: Hyper-V 0x800700B7 'Cannot create a file when that file already exists' - proven by an elevated test (18:5x) to be two Extended ACL rules with the same Direction+Weight on a live switch port; unique weights and IPv6 rules are accepted. Fix: Set-WorkbenchNetworkIsolation.ps1 1.1.0 gives every rule its own weight (Outbound deny 50-56, Inbound deny 40-46, host 60+, ExtraAllow 80+, Inbound hands 101) and refuses a plan with a duplicate before touching the switch. 18:58 run 2: Apply 21 rules read back, Show inventory MATCHES, Connect -&gt; SwitchName Default Switch, Connected True, VM Off. Behaviour proof (Test-WorkbenchIsolation.ps1) still pending until the guest runs.</t>
+          <t>Code done 18-10-2026: Extended Port ACLs deny RFC1918 + link-local + IPv6 ULA/link-local in and out; guest may reach the host (Default Switch gateway) ONLY for DNS (53) and hands-service replies, so host SMB/RDP/dev servers stay unreachable from the guest; public internet stays open; Connect refuses unless the deny rules are present and the gateway is unchanged. Test-WorkbenchIsolation.ps1 proves it over PowerShell Direct. UNVERIFIED on Hyper-V until the local session runs Apply then Test. Known: Default Switch subnet can change after a host reboot; re-Apply then. | 21-10-2026 18:49 first Connect FAILED: Hyper-V 0x800700B7 'Cannot create a file when that file already exists' - proven by an elevated test (18:5x) to be two Extended ACL rules with the same Direction+Weight on a live switch port; unique weights and IPv6 rules are accepted. Fix: Set-WorkbenchNetworkIsolation.ps1 1.1.0 gives every rule its own weight (Outbound deny 50-56, Inbound deny 40-46, host 60+, ExtraAllow 80+, Inbound hands 101) and refuses a plan with a duplicate before touching the switch. 18:58 run 2: Apply 21 rules read back, Show inventory MATCHES, Connect -&gt; SwitchName Default Switch, Connected True, VM Off. Behaviour proof (Test-WorkbenchIsolation.ps1) still pending until the guest runs. | 21-10-2026 23:46 Test-WorkbenchIsolation.ps1 from inside the guest = NOT MEASURED (exit 2): every LAN and internet row failed instantly, DNS failed - the guest had NO internet, so blocked rows prove nothing. Cause measured on the host: a second host boot at 22:36 gave the Default Switch a NEW gateway 172.26.32.1/20 (rules built for 172.17.224.1); the new gateway sits inside the denied 172.16.0.0/12 range, so DHCP/DNS/NAT die. Heal = Apply again for the live gateway + ipconfig /renew in the guest; the minder now does this at every run.</t>
         </is>
       </c>
     </row>

--- a/agent-workbench/TRACKER.xlsx
+++ b/agent-workbench/TRACKER.xlsx
@@ -930,7 +930,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>DECIDED (Architect 18-10-2026): guest-to-LAN block comes BEFORE the first network-connected guest boot. Mechanism: Hyper-V Extended Port ACLs on the VM adapter (host-enforced, the guest cannot lift them). Scripts: host/Set-WorkbenchNetworkIsolation.ps1 (Apply/Show/Remove/Connect/Disconnect) and host/Test-WorkbenchIsolation.ps1 (PowerShell Direct proof from inside the guest). New-Workbench now creates the adapter DISCONNECTED. Guest-only Git identity still owed.</t>
+          <t>DECIDED (Architect 18-10-2026): guest-to-LAN block comes BEFORE the first network-connected guest boot. Mechanism: Hyper-V Extended Port ACLs on the VM adapter (host-enforced, the guest cannot lift them). Scripts: host/Set-WorkbenchNetworkIsolation.ps1 (Apply/Show/Remove/Connect/Disconnect) and host/Test-WorkbenchIsolation.ps1 (PowerShell Direct proof from inside the guest). New-Workbench now creates the adapter DISCONNECTED. Guest-only Git identity still owed. | 22-10-2026: guest-only local account (record on the PC only), no host drive shares, office LAN blocked and VERIFIED from inside the guest; hands service bound to the host gateway only.</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2 runs</t>
+          <t>3 runs</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Code done 18-10-2026: Extended Port ACLs deny RFC1918 + link-local + IPv6 ULA/link-local in and out; guest may reach the host (Default Switch gateway) ONLY for DNS (53) and hands-service replies, so host SMB/RDP/dev servers stay unreachable from the guest; public internet stays open; Connect refuses unless the deny rules are present and the gateway is unchanged. Test-WorkbenchIsolation.ps1 proves it over PowerShell Direct. UNVERIFIED on Hyper-V until the local session runs Apply then Test. Known: Default Switch subnet can change after a host reboot; re-Apply then. | 21-10-2026 18:49 first Connect FAILED: Hyper-V 0x800700B7 'Cannot create a file when that file already exists' - proven by an elevated test (18:5x) to be two Extended ACL rules with the same Direction+Weight on a live switch port; unique weights and IPv6 rules are accepted. Fix: Set-WorkbenchNetworkIsolation.ps1 1.1.0 gives every rule its own weight (Outbound deny 50-56, Inbound deny 40-46, host 60+, ExtraAllow 80+, Inbound hands 101) and refuses a plan with a duplicate before touching the switch. 18:58 run 2: Apply 21 rules read back, Show inventory MATCHES, Connect -&gt; SwitchName Default Switch, Connected True, VM Off. Behaviour proof (Test-WorkbenchIsolation.ps1) still pending until the guest runs. | 21-10-2026 23:46 Test-WorkbenchIsolation.ps1 from inside the guest = NOT MEASURED (exit 2): every LAN and internet row failed instantly, DNS failed - the guest had NO internet, so blocked rows prove nothing. Cause measured on the host: a second host boot at 22:36 gave the Default Switch a NEW gateway 172.26.32.1/20 (rules built for 172.17.224.1); the new gateway sits inside the denied 172.16.0.0/12 range, so DHCP/DNS/NAT die. Heal = Apply again for the live gateway + ipconfig /renew in the guest; the minder now does this at every run.</t>
+          <t>Code done 18-10-2026: Extended Port ACLs deny RFC1918 + link-local + IPv6 ULA/link-local in and out; guest may reach the host (Default Switch gateway) ONLY for DNS (53) and hands-service replies, so host SMB/RDP/dev servers stay unreachable from the guest; public internet stays open; Connect refuses unless the deny rules are present and the gateway is unchanged. Test-WorkbenchIsolation.ps1 proves it over PowerShell Direct. UNVERIFIED on Hyper-V until the local session runs Apply then Test. Known: Default Switch subnet can change after a host reboot; re-Apply then. | 21-10-2026 18:49 first Connect FAILED: Hyper-V 0x800700B7 'Cannot create a file when that file already exists' - proven by an elevated test (18:5x) to be two Extended ACL rules with the same Direction+Weight on a live switch port; unique weights and IPv6 rules are accepted. Fix: Set-WorkbenchNetworkIsolation.ps1 1.1.0 gives every rule its own weight (Outbound deny 50-56, Inbound deny 40-46, host 60+, ExtraAllow 80+, Inbound hands 101) and refuses a plan with a duplicate before touching the switch. 18:58 run 2: Apply 21 rules read back, Show inventory MATCHES, Connect -&gt; SwitchName Default Switch, Connected True, VM Off. Behaviour proof (Test-WorkbenchIsolation.ps1) still pending until the guest runs. | 21-10-2026 23:46 Test-WorkbenchIsolation.ps1 from inside the guest = NOT MEASURED (exit 2): every LAN and internet row failed instantly, DNS failed - the guest had NO internet, so blocked rows prove nothing. Cause measured on the host: a second host boot at 22:36 gave the Default Switch a NEW gateway 172.26.32.1/20 (rules built for 172.17.224.1); the new gateway sits inside the denied 172.16.0.0/12 range, so DHCP/DNS/NAT die. Heal = Apply again for the live gateway + ipconfig /renew in the guest; the minder now does this at every run. | 22-10-2026 00:01 ISOLATION VERIFIED (Test-WorkbenchIsolation.ps1 exit 0, from inside the guest over PowerShell Direct, after the heal: Disconnect, Apply for the live gateway 172.26.32.1, Show, Connect, ipconfig /renew): host ACL baseline 10 deny rules present; LAN 10.199.27.85 / 192.168.1.10 / 192.168.1.254 on TCP 445 + 3389 timed out 21-24 s each and ICMP no reply; host gateway 445/3389 no answer; internet 1.1.1.1 + 8.8.8.8 TCP 443 connected 0-0.1 s; DNS www.microsoft.com resolved 23.37.86.48. Report %LOCALAPPDATA%\Avni\reports\workbench-isolation-test-21-10-2026_2357.json. LESSON: this PC is powered off nightly and the Default Switch gateway changes on boot - run Disconnect/Apply/Connect (step-fg-minder3) before every use; a fixed-gateway internal NAT switch is the proper follow-up.</t>
         </is>
       </c>
     </row>
